--- a/financas/trackfleet_financas.xlsx
+++ b/financas/trackfleet_financas.xlsx
@@ -9,11 +9,12 @@
   <sheets>
     <sheet name="Planejar" sheetId="1" state="visible" r:id="rId1"/>
     <sheet name="Estimar" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="Orçar" sheetId="3" state="visible" r:id="rId3"/>
-    <sheet name="Financiar" sheetId="4" state="visible" r:id="rId4"/>
-    <sheet name="Gerenciar" sheetId="5" state="visible" r:id="rId5"/>
-    <sheet name="Medir" sheetId="6" state="visible" r:id="rId6"/>
-    <sheet name="Controlar custos" sheetId="7" state="visible" r:id="rId7"/>
+    <sheet name="Riscos" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet name="Orçar" sheetId="4" state="visible" r:id="rId4"/>
+    <sheet name="Financiar" sheetId="5" state="visible" r:id="rId5"/>
+    <sheet name="Gerenciar" sheetId="6" state="visible" r:id="rId6"/>
+    <sheet name="Medir" sheetId="7" state="visible" r:id="rId7"/>
+    <sheet name="Controlar custos" sheetId="8" state="visible" r:id="rId8"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -22,8 +23,10 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <numFmts count="1">
+  <numFmts count="3">
     <numFmt numFmtId="164" formatCode="R$ #,##0"/>
+    <numFmt numFmtId="165" formatCode="R$ #,##0;-R$ #,##0"/>
+    <numFmt numFmtId="166" formatCode="0.0%"/>
   </numFmts>
   <fonts count="6">
     <font>
@@ -153,7 +156,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="16">
+  <cellXfs count="23">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
@@ -193,6 +196,27 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="5" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="2" fontId="4" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="2" fontId="3" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="9" fontId="4" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="165" fontId="4" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="165" fontId="3" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="164" fontId="3" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="166" fontId="4" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right" vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -660,9 +684,10 @@
           <t>R$ 300,00</t>
         </is>
       </c>
-      <c r="C8" s="4">
-        <f> 50 x 6. Ponte entre o Cronograma (dias) e as Finanças (reais).</f>
-        <v/>
+      <c r="C8" s="4" t="inlineStr">
+        <is>
+          <t>Igual a 50 x 6. Ponte entre o Cronograma (dias) e as Finanças (reais).</t>
+        </is>
       </c>
     </row>
     <row r="9" ht="30" customHeight="1">
@@ -731,7 +756,7 @@
       </c>
       <c r="B14" s="4" t="inlineStr">
         <is>
-          <t>Dois GPs (é para riscos conhecidos)</t>
+          <t>Dois GPs (é para riscos conhecidos do registro de riscos)</t>
         </is>
       </c>
       <c r="C14" s="4" t="inlineStr">
@@ -788,7 +813,7 @@
           <t>Ação corretiva imediata dos GPs, focada primeiro no caminho crítico.</t>
         </is>
       </c>
-      <c r="C19" s="6" t="n"/>
+      <c r="C19" s="5" t="n"/>
     </row>
     <row r="20" ht="30" customHeight="1">
       <c r="A20" s="4" t="inlineStr">
@@ -801,7 +826,7 @@
           <t>Revisão formal e alerta ao patrocinador; acima da reserva, escalonamento e re-baseline.</t>
         </is>
       </c>
-      <c r="C20" s="6" t="n"/>
+      <c r="C20" s="5" t="n"/>
     </row>
     <row r="21" ht="30" customHeight="1">
       <c r="A21" s="4" t="inlineStr">
@@ -814,7 +839,7 @@
           <t>Reavaliação das estimativas restantes no check-in seguinte.</t>
         </is>
       </c>
-      <c r="C21" s="6" t="n"/>
+      <c r="C21" s="5" t="n"/>
     </row>
   </sheetData>
   <mergeCells count="8">
@@ -837,27 +862,28 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E23"/>
+  <dimension ref="A1:F24"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="30" customWidth="1" min="1" max="1"/>
-    <col width="40" customWidth="1" min="2" max="2"/>
+    <col width="52" customWidth="1" min="2" max="2"/>
     <col width="15" customWidth="1" min="3" max="3"/>
     <col width="14" customWidth="1" min="4" max="4"/>
     <col width="15" customWidth="1" min="5" max="5"/>
+    <col width="18" customWidth="1" min="6" max="6"/>
   </cols>
   <sheetData>
     <row r="1" ht="26" customHeight="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>2. ESTIMAR CUSTOS — Estimativa por pacote da EAP (custo-hora R$ 300/dia-pessoa)</t>
+          <t>2. ESTIMAR CUSTOS — Estimativa por pacote da EAP, a partir das atividades do Cronograma (R$ 300/dia-pessoa)</t>
         </is>
       </c>
     </row>
     <row r="3" ht="20" customHeight="1">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>Estimativa bottom-up por pacote</t>
+          <t>Estimativa bottom-up por pacote (dias-pessoa somados das atividades do Cronograma nivelado)</t>
         </is>
       </c>
     </row>
@@ -869,7 +895,7 @@
       </c>
       <c r="B4" s="3" t="inlineStr">
         <is>
-          <t>Conteúdo</t>
+          <t>Atividades do Cronograma</t>
         </is>
       </c>
       <c r="C4" s="3" t="inlineStr">
@@ -896,7 +922,7 @@
       </c>
       <c r="B5" s="4" t="inlineStr">
         <is>
-          <t>Termo, governança, arquitetura e acompanhamento</t>
+          <t>Esforço contínuo de gestão (fora da rede)</t>
         </is>
       </c>
       <c r="C5" s="4" t="inlineStr">
@@ -904,23 +930,24 @@
           <t>Análoga</t>
         </is>
       </c>
-      <c r="D5" s="7">
-        <f>E5/300</f>
-        <v/>
-      </c>
-      <c r="E5" s="8" t="n">
-        <v>3600</v>
+      <c r="D5" s="16">
+        <f>12</f>
+        <v/>
+      </c>
+      <c r="E5" s="8">
+        <f>ROUND(D5*300,0)</f>
+        <v/>
       </c>
     </row>
     <row r="6" ht="28" customHeight="1">
       <c r="A6" s="4" t="inlineStr">
         <is>
-          <t>1.2 Requisitos</t>
+          <t>1.2 Requisitos e Arquitetura</t>
         </is>
       </c>
       <c r="B6" s="4" t="inlineStr">
         <is>
-          <t>Entrevistas e especificação</t>
+          <t>A1 (dois GPs, 3 d), A2 (2 d), A3 (3 d), A4 (2 d)</t>
         </is>
       </c>
       <c r="C6" s="4" t="inlineStr">
@@ -928,12 +955,13 @@
           <t>Análoga</t>
         </is>
       </c>
-      <c r="D6" s="7">
-        <f>E6/300</f>
-        <v/>
-      </c>
-      <c r="E6" s="8" t="n">
-        <v>3000</v>
+      <c r="D6" s="16">
+        <f>3*2+2+3+2</f>
+        <v/>
+      </c>
+      <c r="E6" s="8">
+        <f>ROUND(D6*300,0)</f>
+        <v/>
       </c>
     </row>
     <row r="7" ht="28" customHeight="1">
@@ -944,7 +972,7 @@
       </c>
       <c r="B7" s="4" t="inlineStr">
         <is>
-          <t>API própria e ingestão das posições</t>
+          <t>A5 (3 d), A6 (6 d), A7 (6 d)</t>
         </is>
       </c>
       <c r="C7" s="4" t="inlineStr">
@@ -952,12 +980,13 @@
           <t>Três pontos</t>
         </is>
       </c>
-      <c r="D7" s="7">
-        <f>E7/300</f>
-        <v/>
-      </c>
-      <c r="E7" s="8" t="n">
-        <v>5550</v>
+      <c r="D7" s="16">
+        <f>3+6+6</f>
+        <v/>
+      </c>
+      <c r="E7" s="8">
+        <f>ROUND(D7*300,0)</f>
+        <v/>
       </c>
     </row>
     <row r="8" ht="28" customHeight="1">
@@ -968,7 +997,7 @@
       </c>
       <c r="B8" s="4" t="inlineStr">
         <is>
-          <t>Os quatro motores do catálogo</t>
+          <t>A8 (9 d)</t>
         </is>
       </c>
       <c r="C8" s="4" t="inlineStr">
@@ -976,12 +1005,13 @@
           <t>Três pontos</t>
         </is>
       </c>
-      <c r="D8" s="7">
-        <f>E8/300</f>
-        <v/>
-      </c>
-      <c r="E8" s="8" t="n">
-        <v>2850</v>
+      <c r="D8" s="16">
+        <f>9</f>
+        <v/>
+      </c>
+      <c r="E8" s="8">
+        <f>ROUND(D8*300,0)</f>
+        <v/>
       </c>
     </row>
     <row r="9" ht="28" customHeight="1">
@@ -992,7 +1022,7 @@
       </c>
       <c r="B9" s="4" t="inlineStr">
         <is>
-          <t>Mapa, painel, cadastros e relatórios</t>
+          <t>A11 (6 d), A12 (4 d), A13 (3 d), A14 (4 d)</t>
         </is>
       </c>
       <c r="C9" s="4" t="inlineStr">
@@ -1000,12 +1030,13 @@
           <t>Paramétrica</t>
         </is>
       </c>
-      <c r="D9" s="7">
-        <f>E9/300</f>
-        <v/>
-      </c>
-      <c r="E9" s="8" t="n">
-        <v>5100</v>
+      <c r="D9" s="16">
+        <f>6+4+3+4</f>
+        <v/>
+      </c>
+      <c r="E9" s="8">
+        <f>ROUND(D9*300,0)</f>
+        <v/>
       </c>
     </row>
     <row r="10" ht="28" customHeight="1">
@@ -1016,7 +1047,7 @@
       </c>
       <c r="B10" s="4" t="inlineStr">
         <is>
-          <t>Perfil de gestor e conformidade</t>
+          <t>A9 (2 d), A10 (3 d)</t>
         </is>
       </c>
       <c r="C10" s="4" t="inlineStr">
@@ -1024,220 +1055,281 @@
           <t>Bottom-up</t>
         </is>
       </c>
-      <c r="D10" s="7">
-        <f>E10/300</f>
-        <v/>
-      </c>
-      <c r="E10" s="8" t="n">
-        <v>1500</v>
+      <c r="D10" s="16">
+        <f>2+3</f>
+        <v/>
+      </c>
+      <c r="E10" s="8">
+        <f>ROUND(D10*300,0)</f>
+        <v/>
       </c>
     </row>
     <row r="11" ht="28" customHeight="1">
       <c r="A11" s="4" t="inlineStr">
         <is>
-          <t>1.4 Testes e Homologação</t>
+          <t>1.3.5 Infraestrutura e implantação</t>
         </is>
       </c>
       <c r="B11" s="4" t="inlineStr">
         <is>
-          <t>Testes e piloto com a transportadora</t>
+          <t>A21 (2 d)</t>
         </is>
       </c>
       <c r="C11" s="4" t="inlineStr">
         <is>
-          <t>Três pontos</t>
-        </is>
-      </c>
-      <c r="D11" s="7">
-        <f>E11/300</f>
-        <v/>
-      </c>
-      <c r="E11" s="8" t="n">
-        <v>4400</v>
+          <t>Especialista</t>
+        </is>
+      </c>
+      <c r="D11" s="16">
+        <f>2</f>
+        <v/>
+      </c>
+      <c r="E11" s="8">
+        <f>ROUND(D11*300,0)</f>
+        <v/>
       </c>
     </row>
     <row r="12" ht="28" customHeight="1">
       <c r="A12" s="4" t="inlineStr">
         <is>
+          <t>1.4 Testes e Homologação</t>
+        </is>
+      </c>
+      <c r="B12" s="4" t="inlineStr">
+        <is>
+          <t>A15 (4 d), A16 (3 d), A17 (3 d), A18 (11 d x 2 GPs x 1/3)</t>
+        </is>
+      </c>
+      <c r="C12" s="4" t="inlineStr">
+        <is>
+          <t>Três pontos</t>
+        </is>
+      </c>
+      <c r="D12" s="16">
+        <f>4+3+3+11*2/3</f>
+        <v/>
+      </c>
+      <c r="E12" s="8">
+        <f>ROUND(D12*300,0)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="4" t="inlineStr">
+        <is>
           <t>1.5 Treinamento e Encerramento</t>
         </is>
       </c>
-      <c r="B12" s="4" t="inlineStr">
-        <is>
-          <t>Treinamento e lições aprendidas</t>
-        </is>
-      </c>
-      <c r="C12" s="4" t="inlineStr">
+      <c r="B13" s="4" t="inlineStr">
+        <is>
+          <t>A19 (1 d x 2 GPs x 2/3), A20 (3 d x 2/3)</t>
+        </is>
+      </c>
+      <c r="C13" s="4" t="inlineStr">
         <is>
           <t>Análoga</t>
         </is>
       </c>
-      <c r="D12" s="7">
-        <f>E12/300</f>
-        <v/>
-      </c>
-      <c r="E12" s="8" t="n">
-        <v>1200</v>
-      </c>
-    </row>
-    <row r="13">
-      <c r="A13" s="9" t="inlineStr">
+      <c r="D13" s="16">
+        <f>1*2*2/3+3*2/3</f>
+        <v/>
+      </c>
+      <c r="E13" s="8">
+        <f>ROUND(D13*300,0)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="9" t="inlineStr">
         <is>
           <t>Subtotal mão de obra (CapEx)</t>
         </is>
       </c>
-      <c r="B13" s="9" t="inlineStr"/>
-      <c r="C13" s="9" t="inlineStr"/>
-      <c r="D13" s="10">
-        <f>SUM(D5:D12)</f>
-        <v/>
-      </c>
-      <c r="E13" s="11">
-        <f>SUM(E5:E12)</f>
-        <v/>
-      </c>
-    </row>
-    <row r="14">
-      <c r="A14" s="4" t="inlineStr">
+      <c r="B14" s="9" t="n"/>
+      <c r="C14" s="9" t="n"/>
+      <c r="D14" s="17">
+        <f>SUM(D5:D13)</f>
+        <v/>
+      </c>
+      <c r="E14" s="11">
+        <f>SUM(E5:E13)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="4" t="inlineStr">
         <is>
           <t>Infraestrutura do período (OpEx)</t>
         </is>
       </c>
-      <c r="B14" s="4" t="inlineStr">
-        <is>
-          <t>API, hospedagem, domínio, TLS</t>
-        </is>
-      </c>
-      <c r="C14" s="4" t="inlineStr">
+      <c r="B15" s="4" t="inlineStr">
+        <is>
+          <t>API, VPS, domínio, ferramentas (aba Financiar)</t>
+        </is>
+      </c>
+      <c r="C15" s="4" t="inlineStr">
         <is>
           <t>Bottom-up</t>
         </is>
       </c>
-      <c r="D14" s="4" t="inlineStr"/>
-      <c r="E14" s="8" t="n">
-        <v>700</v>
-      </c>
-    </row>
-    <row r="15">
-      <c r="A15" s="9" t="inlineStr">
+      <c r="D15" s="4" t="n"/>
+      <c r="E15" s="8">
+        <f>Financiar!D26</f>
+        <v/>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="9" t="inlineStr">
         <is>
           <t>Total das estimativas</t>
         </is>
       </c>
-      <c r="B15" s="9" t="inlineStr"/>
-      <c r="C15" s="9" t="inlineStr"/>
-      <c r="D15" s="9" t="inlineStr"/>
-      <c r="E15" s="11">
-        <f>E13+E14</f>
+      <c r="B16" s="9" t="n"/>
+      <c r="C16" s="9" t="n"/>
+      <c r="D16" s="9" t="n"/>
+      <c r="E16" s="11">
+        <f>E14+E15</f>
         <v/>
       </c>
     </row>
     <row r="17" ht="20" customHeight="1">
-      <c r="A17" s="2" t="inlineStr">
-        <is>
-          <t>Estimativa de três pontos dos pacotes de risco — C_E = (O + 4M + P) / 6</t>
-        </is>
-      </c>
+      <c r="A17" s="2" t="n"/>
     </row>
     <row r="18">
-      <c r="A18" s="3" t="inlineStr">
+      <c r="A18" s="2" t="inlineStr">
+        <is>
+          <t>Estimativa de três pontos dos pacotes de risco — C_E = (O + 4M + P) / 6, a partir do O/M/P das atividades do Cronograma</t>
+        </is>
+      </c>
+    </row>
+    <row r="19" ht="22" customHeight="1">
+      <c r="A19" s="3" t="inlineStr">
         <is>
           <t>Pacote</t>
         </is>
       </c>
-      <c r="B18" s="3" t="inlineStr">
+      <c r="B19" s="3" t="inlineStr">
         <is>
           <t>Otimista (R$)</t>
         </is>
       </c>
-      <c r="C18" s="3" t="inlineStr">
+      <c r="C19" s="3" t="inlineStr">
         <is>
           <t>Mais provável (R$)</t>
         </is>
       </c>
-      <c r="D18" s="3" t="inlineStr">
+      <c r="D19" s="3" t="inlineStr">
         <is>
           <t>Pessimista (R$)</t>
         </is>
       </c>
-      <c r="E18" s="3" t="inlineStr">
+      <c r="E19" s="3" t="inlineStr">
         <is>
           <t>Estimado C_E (R$)</t>
         </is>
       </c>
-    </row>
-    <row r="19" ht="22" customHeight="1">
-      <c r="A19" s="4" t="inlineStr">
-        <is>
-          <t>1.3.1 Backend, API e ingestão</t>
-        </is>
-      </c>
-      <c r="B19" s="8" t="n">
-        <v>3600</v>
-      </c>
-      <c r="C19" s="8" t="n">
-        <v>5400</v>
-      </c>
-      <c r="D19" s="8" t="n">
-        <v>8100</v>
-      </c>
-      <c r="E19" s="8">
-        <f>(B19+4*C19+D19)/6</f>
-        <v/>
+      <c r="F19" t="inlineStr">
+        <is>
+          <t>Na linha de base (R$)</t>
+        </is>
       </c>
     </row>
     <row r="20" ht="22" customHeight="1">
       <c r="A20" s="4" t="inlineStr">
         <is>
-          <t>1.3.2 Motor de alertas</t>
-        </is>
-      </c>
-      <c r="B20" s="8" t="n">
-        <v>1800</v>
-      </c>
-      <c r="C20" s="8" t="n">
-        <v>2700</v>
-      </c>
-      <c r="D20" s="8" t="n">
-        <v>4500</v>
+          <t>1.3.1 Backend, API e ingestão</t>
+        </is>
+      </c>
+      <c r="B20" s="8">
+        <f>(3+3+3)*300</f>
+        <v/>
+      </c>
+      <c r="C20" s="8">
+        <f>(3+5+5)*300</f>
+        <v/>
+      </c>
+      <c r="D20" s="8">
+        <f>(3+9+10)*300</f>
+        <v/>
       </c>
       <c r="E20" s="8">
         <f>(B20+4*C20+D20)/6</f>
         <v/>
       </c>
+      <c r="F20">
+        <f>E7</f>
+        <v/>
+      </c>
     </row>
     <row r="21" ht="22" customHeight="1">
       <c r="A21" s="4" t="inlineStr">
         <is>
-          <t>1.4 Testes e Homologação</t>
-        </is>
-      </c>
-      <c r="B21" s="8" t="n">
-        <v>3000</v>
-      </c>
-      <c r="C21" s="8" t="n">
-        <v>4200</v>
-      </c>
-      <c r="D21" s="8" t="n">
-        <v>6600</v>
+          <t>1.3.2 Motor de alertas</t>
+        </is>
+      </c>
+      <c r="B21" s="8">
+        <f>5*300</f>
+        <v/>
+      </c>
+      <c r="C21" s="8">
+        <f>8*300</f>
+        <v/>
+      </c>
+      <c r="D21" s="8">
+        <f>15*300</f>
+        <v/>
       </c>
       <c r="E21" s="8">
         <f>(B21+4*C21+D21)/6</f>
         <v/>
       </c>
+      <c r="F21">
+        <f>E8</f>
+        <v/>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" s="4" t="inlineStr">
+        <is>
+          <t>1.4 Testes e Homologação</t>
+        </is>
+      </c>
+      <c r="B22" s="8">
+        <f>(10+7*2/3)*300</f>
+        <v/>
+      </c>
+      <c r="C22" s="8">
+        <f>(10+10*2/3)*300</f>
+        <v/>
+      </c>
+      <c r="D22" s="8">
+        <f>(10+15*2/3)*300</f>
+        <v/>
+      </c>
+      <c r="E22" s="8">
+        <f>(B22+4*C22+D22)/6</f>
+        <v/>
+      </c>
+      <c r="F22">
+        <f>E12</f>
+        <v/>
+      </c>
     </row>
     <row r="23" ht="30" customHeight="1">
-      <c r="A23" s="12" t="inlineStr">
-        <is>
-          <t>A distância entre otimista e pessimista mede o risco do pacote — é o que dimensiona a reserva de contingência da aba Orçar. O Backend depende de API externa; o Motor de alertas reúne quatro lógicas de disparo.</t>
+      <c r="A23" s="12" t="n"/>
+    </row>
+    <row r="24">
+      <c r="A24" s="12" t="inlineStr">
+        <is>
+          <t>A linha de base usa as durações do Cronograma com t_E arredondado para cima; por isso fica acima de C_E. A incerteza dos pacotes é tratada no registro de riscos (aba Riscos), que dimensiona a reserva de contingência.</t>
         </is>
       </c>
     </row>
   </sheetData>
   <mergeCells count="4">
+    <mergeCell ref="A24:F24"/>
     <mergeCell ref="A1:E1"/>
-    <mergeCell ref="A23:E23"/>
-    <mergeCell ref="A17:E17"/>
+    <mergeCell ref="A18:F18"/>
     <mergeCell ref="A3:E3"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -1250,7 +1342,379 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D32"/>
+  <dimension ref="A1:F17"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="8" customWidth="1" min="1" max="1"/>
+    <col width="62" customWidth="1" min="2" max="2"/>
+    <col width="14" customWidth="1" min="3" max="3"/>
+    <col width="14" customWidth="1" min="4" max="4"/>
+    <col width="14" customWidth="1" min="5" max="5"/>
+    <col width="12" customWidth="1" min="6" max="6"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>RISCOS — Valor Monetário Esperado (VME) que dimensiona a reserva de contingência</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" s="3" t="inlineStr">
+        <is>
+          <t>ID</t>
+        </is>
+      </c>
+      <c r="B3" s="3" t="inlineStr">
+        <is>
+          <t>Risco (resumo)</t>
+        </is>
+      </c>
+      <c r="C3" s="3" t="inlineStr">
+        <is>
+          <t>Probabilidade</t>
+        </is>
+      </c>
+      <c r="D3" s="3" t="inlineStr">
+        <is>
+          <t>Impacto (R$)</t>
+        </is>
+      </c>
+      <c r="E3" s="3" t="inlineStr">
+        <is>
+          <t>VME (R$)</t>
+        </is>
+      </c>
+      <c r="F3" s="3" t="inlineStr">
+        <is>
+          <t>Dono</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="4" t="inlineStr">
+        <is>
+          <t>R01</t>
+        </is>
+      </c>
+      <c r="B4" s="4" t="inlineStr">
+        <is>
+          <t>Acesso, documentação ou limite da API do provedor atrasam a ingestão (A7)</t>
+        </is>
+      </c>
+      <c r="C4" s="18" t="n">
+        <v>0.7</v>
+      </c>
+      <c r="D4" s="19" t="n">
+        <v>-1800</v>
+      </c>
+      <c r="E4" s="19">
+        <f>C4*D4</f>
+        <v/>
+      </c>
+      <c r="F4" s="4" t="inlineStr">
+        <is>
+          <t>Kerlon</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="4" t="inlineStr">
+        <is>
+          <t>R02</t>
+        </is>
+      </c>
+      <c r="B5" s="4" t="inlineStr">
+        <is>
+          <t>Motor de alertas (A8) estoura além do pessimista</t>
+        </is>
+      </c>
+      <c r="C5" s="18" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="D5" s="19" t="n">
+        <v>-1500</v>
+      </c>
+      <c r="E5" s="19">
+        <f>C5*D5</f>
+        <v/>
+      </c>
+      <c r="F5" s="4" t="inlineStr">
+        <is>
+          <t>Enzo</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="4" t="inlineStr">
+        <is>
+          <t>R03</t>
+        </is>
+      </c>
+      <c r="B6" s="4" t="inlineStr">
+        <is>
+          <t>Não conformidade com a LGPD exige retrabalho e trava o piloto</t>
+        </is>
+      </c>
+      <c r="C6" s="18" t="n">
+        <v>0.3</v>
+      </c>
+      <c r="D6" s="19" t="n">
+        <v>-2400</v>
+      </c>
+      <c r="E6" s="19">
+        <f>C6*D6</f>
+        <v/>
+      </c>
+      <c r="F6" s="4" t="inlineStr">
+        <is>
+          <t>Kerlon</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="4" t="inlineStr">
+        <is>
+          <t>R04</t>
+        </is>
+      </c>
+      <c r="B7" s="4" t="inlineStr">
+        <is>
+          <t>Sobrecarga dos GPs com provas e outras disciplinas</t>
+        </is>
+      </c>
+      <c r="C7" s="18" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="D7" s="19" t="n">
+        <v>-1200</v>
+      </c>
+      <c r="E7" s="19">
+        <f>C7*D7</f>
+        <v/>
+      </c>
+      <c r="F7" s="4" t="inlineStr">
+        <is>
+          <t>Enzo</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="4" t="inlineStr">
+        <is>
+          <t>R05</t>
+        </is>
+      </c>
+      <c r="B8" s="4" t="inlineStr">
+        <is>
+          <t>Transportadora atrasa ou usa pouco o piloto, que precisa ser estendido</t>
+        </is>
+      </c>
+      <c r="C8" s="18" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="D8" s="19" t="n">
+        <v>-800</v>
+      </c>
+      <c r="E8" s="19">
+        <f>C8*D8</f>
+        <v/>
+      </c>
+      <c r="F8" s="4" t="inlineStr">
+        <is>
+          <t>Kerlon</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="4" t="inlineStr">
+        <is>
+          <t>R06</t>
+        </is>
+      </c>
+      <c r="B9" s="4" t="inlineStr">
+        <is>
+          <t>Patrocinador demora a aprovar marcos</t>
+        </is>
+      </c>
+      <c r="C9" s="18" t="n">
+        <v>0.3</v>
+      </c>
+      <c r="D9" s="19" t="n">
+        <v>-600</v>
+      </c>
+      <c r="E9" s="19">
+        <f>C9*D9</f>
+        <v/>
+      </c>
+      <c r="F9" s="4" t="inlineStr">
+        <is>
+          <t>Enzo</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="4" t="inlineStr">
+        <is>
+          <t>R07</t>
+        </is>
+      </c>
+      <c r="B10" s="4" t="inlineStr">
+        <is>
+          <t>Resistência dos motoristas (rastreador desligado, dados falhos)</t>
+        </is>
+      </c>
+      <c r="C10" s="18" t="n">
+        <v>0.3</v>
+      </c>
+      <c r="D10" s="19" t="n">
+        <v>-900</v>
+      </c>
+      <c r="E10" s="19">
+        <f>C10*D10</f>
+        <v/>
+      </c>
+      <c r="F10" s="4" t="inlineStr">
+        <is>
+          <t>Kerlon</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="4" t="inlineStr">
+        <is>
+          <t>R08</t>
+        </is>
+      </c>
+      <c r="B11" s="4" t="inlineStr">
+        <is>
+          <t>Intervalo irregular do provedor gera alertas falsos de perda de sinal</t>
+        </is>
+      </c>
+      <c r="C11" s="18" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="D11" s="19" t="n">
+        <v>-600</v>
+      </c>
+      <c r="E11" s="19">
+        <f>C11*D11</f>
+        <v/>
+      </c>
+      <c r="F11" s="4" t="inlineStr">
+        <is>
+          <t>Kerlon</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="4" t="inlineStr">
+        <is>
+          <t>O01</t>
+        </is>
+      </c>
+      <c r="B12" s="4" t="inlineStr">
+        <is>
+          <t>Bibliotecas prontas de exportação PDF/XLS reduzem A14</t>
+        </is>
+      </c>
+      <c r="C12" s="18" t="n">
+        <v>0.7</v>
+      </c>
+      <c r="D12" s="19" t="n">
+        <v>600</v>
+      </c>
+      <c r="E12" s="19">
+        <f>C12*D12</f>
+        <v/>
+      </c>
+      <c r="F12" s="4" t="inlineStr">
+        <is>
+          <t>Enzo</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="4" t="inlineStr">
+        <is>
+          <t>O02</t>
+        </is>
+      </c>
+      <c r="B13" s="4" t="inlineStr">
+        <is>
+          <t>Webhook do provedor substitui o polling e reduz A7</t>
+        </is>
+      </c>
+      <c r="C13" s="18" t="n">
+        <v>0.3</v>
+      </c>
+      <c r="D13" s="19" t="n">
+        <v>300</v>
+      </c>
+      <c r="E13" s="19">
+        <f>C13*D13</f>
+        <v/>
+      </c>
+      <c r="F13" s="4" t="inlineStr">
+        <is>
+          <t>Kerlon</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="9" t="inlineStr">
+        <is>
+          <t>Total (VME líquido)</t>
+        </is>
+      </c>
+      <c r="B14" s="9" t="n"/>
+      <c r="C14" s="9" t="n"/>
+      <c r="D14" s="9" t="n"/>
+      <c r="E14" s="20">
+        <f>SUM(E4:E13)</f>
+        <v/>
+      </c>
+      <c r="F14" s="9" t="n"/>
+    </row>
+    <row r="15">
+      <c r="A15" s="9" t="inlineStr">
+        <is>
+          <t>Reserva de contingência (valor absoluto do VME líquido)</t>
+        </is>
+      </c>
+      <c r="B15" s="9" t="n"/>
+      <c r="C15" s="9" t="n"/>
+      <c r="D15" s="9" t="n"/>
+      <c r="E15" s="21">
+        <f>-E14</f>
+        <v/>
+      </c>
+      <c r="F15" s="9" t="n"/>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>Escalas e respostas completas no Documento de Riscos (riscos/). Ameaças têm impacto negativo; oportunidades, positivo. O03 (escalar ao portfólio) não entra no VME por gerar valor fora do projeto.</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <mergeCells count="2">
+    <mergeCell ref="A1:F1"/>
+    <mergeCell ref="A17:F17"/>
+  </mergeCells>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:D34"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="40" customWidth="1" min="1" max="1"/>
@@ -1298,7 +1762,7 @@
       </c>
       <c r="B5" s="4" t="inlineStr">
         <is>
-          <t>Estouros previsíveis das frentes de risco (Backend/API e Motor de alertas)</t>
+          <t>Riscos do registro de riscos, pelo VME líquido (aba Riscos)</t>
         </is>
       </c>
       <c r="C5" s="4" t="inlineStr">
@@ -1350,8 +1814,9 @@
           <t>Estimativas dos pacotes (mão de obra)</t>
         </is>
       </c>
-      <c r="B10" s="8" t="n">
-        <v>27200</v>
+      <c r="B10" s="8">
+        <f>Estimar!E14</f>
+        <v/>
       </c>
       <c r="C10" s="4" t="inlineStr"/>
     </row>
@@ -1361,8 +1826,9 @@
           <t>Infraestrutura do período (OpEx)</t>
         </is>
       </c>
-      <c r="B11" s="8" t="n">
-        <v>700</v>
+      <c r="B11" s="8">
+        <f>Estimar!E15</f>
+        <v/>
       </c>
       <c r="C11" s="4" t="inlineStr"/>
     </row>
@@ -1381,11 +1847,11 @@
     <row r="13">
       <c r="A13" s="4" t="inlineStr">
         <is>
-          <t>(+) Reserva de contingência (10% das estimativas)</t>
+          <t>(+) Reserva de contingência (VME líquido do registro de riscos)</t>
         </is>
       </c>
       <c r="B13" s="8">
-        <f>ROUND(B12*0.1,0)</f>
+        <f>Riscos!E15</f>
         <v/>
       </c>
       <c r="C13" s="4" t="inlineStr"/>
@@ -1436,7 +1902,7 @@
     <row r="20" ht="20" customHeight="1">
       <c r="A20" s="2" t="inlineStr">
         <is>
-          <t>Orçamento no tempo — Curva S (Valor Planejado acumulado sobre as 10 semanas)</t>
+          <t>Orçamento no tempo — Curva S (Valor Planejado acumulado sobre as 11 semanas do Cronograma nivelado)</t>
         </is>
       </c>
     </row>
@@ -1460,11 +1926,11 @@
     <row r="22">
       <c r="A22" s="4" t="inlineStr">
         <is>
-          <t>S1</t>
-        </is>
-      </c>
-      <c r="B22" s="13" t="n">
-        <v>0.05</v>
+          <t>S1 (31/08)</t>
+        </is>
+      </c>
+      <c r="B22" s="22" t="n">
+        <v>0.11774</v>
       </c>
       <c r="C22" s="8">
         <f>ROUND($B$14*B22,0)</f>
@@ -1474,11 +1940,11 @@
     <row r="23">
       <c r="A23" s="4" t="inlineStr">
         <is>
-          <t>S2</t>
-        </is>
-      </c>
-      <c r="B23" s="13" t="n">
-        <v>0.12</v>
+          <t>S2 (07/09)</t>
+        </is>
+      </c>
+      <c r="B23" s="22" t="n">
+        <v>0.20423</v>
       </c>
       <c r="C23" s="8">
         <f>ROUND($B$14*B23,0)</f>
@@ -1488,11 +1954,11 @@
     <row r="24">
       <c r="A24" s="4" t="inlineStr">
         <is>
-          <t>S3</t>
-        </is>
-      </c>
-      <c r="B24" s="13" t="n">
-        <v>0.22</v>
+          <t>S3 (14/09)</t>
+        </is>
+      </c>
+      <c r="B24" s="22" t="n">
+        <v>0.32197</v>
       </c>
       <c r="C24" s="8">
         <f>ROUND($B$14*B24,0)</f>
@@ -1502,11 +1968,11 @@
     <row r="25">
       <c r="A25" s="4" t="inlineStr">
         <is>
-          <t>S4</t>
-        </is>
-      </c>
-      <c r="B25" s="13" t="n">
-        <v>0.36</v>
+          <t>S4 (21/09)</t>
+        </is>
+      </c>
+      <c r="B25" s="22" t="n">
+        <v>0.43971</v>
       </c>
       <c r="C25" s="8">
         <f>ROUND($B$14*B25,0)</f>
@@ -1516,11 +1982,11 @@
     <row r="26">
       <c r="A26" s="4" t="inlineStr">
         <is>
-          <t>S5</t>
-        </is>
-      </c>
-      <c r="B26" s="13" t="n">
-        <v>0.5</v>
+          <t>S5 (28/09)</t>
+        </is>
+      </c>
+      <c r="B26" s="22" t="n">
+        <v>0.557449</v>
       </c>
       <c r="C26" s="8">
         <f>ROUND($B$14*B26,0)</f>
@@ -1530,11 +1996,11 @@
     <row r="27">
       <c r="A27" s="4" t="inlineStr">
         <is>
-          <t>S6</t>
-        </is>
-      </c>
-      <c r="B27" s="13" t="n">
-        <v>0.6</v>
+          <t>S6 (05/10)</t>
+        </is>
+      </c>
+      <c r="B27" s="22" t="n">
+        <v>0.675189</v>
       </c>
       <c r="C27" s="8">
         <f>ROUND($B$14*B27,0)</f>
@@ -1544,11 +2010,11 @@
     <row r="28">
       <c r="A28" s="4" t="inlineStr">
         <is>
-          <t>S7</t>
-        </is>
-      </c>
-      <c r="B28" s="13" t="n">
-        <v>0.74</v>
+          <t>S7 (12/10)</t>
+        </is>
+      </c>
+      <c r="B28" s="22" t="n">
+        <v>0.772096</v>
       </c>
       <c r="C28" s="8">
         <f>ROUND($B$14*B28,0)</f>
@@ -1558,11 +2024,11 @@
     <row r="29">
       <c r="A29" s="4" t="inlineStr">
         <is>
-          <t>S8</t>
-        </is>
-      </c>
-      <c r="B29" s="13" t="n">
-        <v>0.86</v>
+          <t>S8 (19/10)</t>
+        </is>
+      </c>
+      <c r="B29" s="22" t="n">
+        <v>0.848169</v>
       </c>
       <c r="C29" s="8">
         <f>ROUND($B$14*B29,0)</f>
@@ -1572,11 +2038,11 @@
     <row r="30">
       <c r="A30" s="4" t="inlineStr">
         <is>
-          <t>S9</t>
-        </is>
-      </c>
-      <c r="B30" s="13" t="n">
-        <v>0.95</v>
+          <t>S9 (26/10)</t>
+        </is>
+      </c>
+      <c r="B30" s="22" t="n">
+        <v>0.896465</v>
       </c>
       <c r="C30" s="8">
         <f>ROUND($B$14*B30,0)</f>
@@ -1586,11 +2052,11 @@
     <row r="31">
       <c r="A31" s="4" t="inlineStr">
         <is>
-          <t>S10</t>
-        </is>
-      </c>
-      <c r="B31" s="13" t="n">
-        <v>1</v>
+          <t>S10 (02/11)</t>
+        </is>
+      </c>
+      <c r="B31" s="22" t="n">
+        <v>0.937816</v>
       </c>
       <c r="C31" s="8">
         <f>ROUND($B$14*B31,0)</f>
@@ -1598,19 +2064,33 @@
       </c>
     </row>
     <row r="32" ht="30" customHeight="1">
-      <c r="A32" s="12" t="inlineStr">
-        <is>
-          <t>Forma de S: gasto lento no arranque, íngreme no miolo do desenvolvimento, achatado no encerramento. Esta curva é o PV usado no exemplo da aba Controlar custos.</t>
+      <c r="A32" s="4" t="inlineStr">
+        <is>
+          <t>S11 (09/11)</t>
+        </is>
+      </c>
+      <c r="B32" s="22" t="n">
+        <v>1</v>
+      </c>
+      <c r="C32" s="8">
+        <f>ROUND($B$14*B32,0)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" s="12" t="inlineStr">
+        <is>
+          <t>Miolo íngreme e fim achatado (no piloto, S9 a S11, a equipe trabalha 1/3 da jornada). O arranque não é lento porque a equipe fixa de dois GPs começa 100% alocada. Esta curva é o PV da aba Controlar custos.</t>
         </is>
       </c>
     </row>
   </sheetData>
   <mergeCells count="7">
     <mergeCell ref="A1:D1"/>
-    <mergeCell ref="A32:C32"/>
     <mergeCell ref="A8:C8"/>
     <mergeCell ref="A18:C18"/>
     <mergeCell ref="A3:C3"/>
+    <mergeCell ref="A34:C34"/>
     <mergeCell ref="B9:C9"/>
     <mergeCell ref="A20:C20"/>
   </mergeCells>
@@ -1618,7 +2098,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -1806,11 +2286,12 @@
       </c>
       <c r="C14" s="4" t="inlineStr">
         <is>
-          <t>Horas de dev, arquitetura e setup inicial</t>
-        </is>
-      </c>
-      <c r="D14" s="8" t="n">
-        <v>27200</v>
+          <t>Horas de trabalho dos GPs em todos os pacotes da EAP</t>
+        </is>
+      </c>
+      <c r="D14" s="8">
+        <f>Estimar!E14</f>
+        <v/>
       </c>
     </row>
     <row r="15" ht="28" customHeight="1">
@@ -1826,11 +2307,12 @@
       </c>
       <c r="C15" s="4" t="inlineStr">
         <is>
-          <t>API, hospedagem, domínio, TLS (grátis)</t>
-        </is>
-      </c>
-      <c r="D15" s="8" t="n">
-        <v>700</v>
+          <t>API, VPS, domínio, ferramentas; TLS e e-mail gratuitos</t>
+        </is>
+      </c>
+      <c r="D15" s="8">
+        <f>D26</f>
+        <v/>
       </c>
     </row>
     <row r="17" ht="30" customHeight="1">
@@ -1981,7 +2463,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -2027,11 +2509,12 @@
     <row r="5">
       <c r="A5" s="4" t="inlineStr">
         <is>
-          <t>Investimento inicial (orçamento total)</t>
-        </is>
-      </c>
-      <c r="B5" s="8" t="n">
-        <v>32225</v>
+          <t>Investimento inicial (orçamento total, inclui o custo de oportunidade das horas da dupla)</t>
+        </is>
+      </c>
+      <c r="B5" s="8">
+        <f>Orçar!B16</f>
+        <v/>
       </c>
       <c r="C5" s="4" t="inlineStr"/>
       <c r="D5" s="4" t="inlineStr"/>
@@ -2347,7 +2830,7 @@
     <row r="31" ht="30" customHeight="1">
       <c r="A31" s="12" t="inlineStr">
         <is>
-          <t>No cenário pessimista o payback fica em torno de 2,4 anos (ainda dentro do horizonte) e o VPL de 3 anos fica no limiar — levemente negativo (~ -R$ 520) —, voltando a positivo num horizonte de 4 anos. A decisão de investir se sustenta, com margem mais estreita.</t>
+          <t>No cenário pessimista o payback fica em torno de 2,6 anos e o VPL de 3 anos fica negativo (~ -R$ 2.705), voltando a positivo num horizonte de 4 anos (~ +R$ 5.684). A decisão de investir se sustenta, com margem mais estreita e dependendo de a plataforma ser usada por mais tempo.</t>
         </is>
       </c>
     </row>
@@ -2415,7 +2898,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -2473,7 +2956,7 @@
       </c>
       <c r="C5" s="4" t="inlineStr">
         <is>
-          <t>A linha de base de custos: R$ 30.690 (aba Orçar).</t>
+          <t>A linha de base de custos: R$ 32.770 (aba Orçar).</t>
         </is>
       </c>
     </row>
@@ -2706,7 +3189,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -2757,8 +3240,9 @@
           <t>BAC — linha de base de custos</t>
         </is>
       </c>
-      <c r="B5" s="8" t="n">
-        <v>30690</v>
+      <c r="B5" s="8">
+        <f>Orçar!B14</f>
+        <v/>
       </c>
       <c r="C5" s="4" t="inlineStr">
         <is>
@@ -2772,12 +3256,13 @@
           <t>% planejado até o corte</t>
         </is>
       </c>
-      <c r="B6" s="13" t="n">
-        <v>0.6</v>
+      <c r="B6" s="13">
+        <f>Orçar!B27</f>
+        <v/>
       </c>
       <c r="C6" s="4" t="inlineStr">
         <is>
-          <t>Curva S no fim da S6</t>
+          <t>Curva S no fim da S6 (09/10)</t>
         </is>
       </c>
     </row>
@@ -2788,7 +3273,7 @@
         </is>
       </c>
       <c r="B7" s="13" t="n">
-        <v>0.55</v>
+        <v>0.62</v>
       </c>
       <c r="C7" s="4" t="inlineStr">
         <is>
@@ -2803,7 +3288,7 @@
         </is>
       </c>
       <c r="B8" s="8" t="n">
-        <v>17600</v>
+        <v>21200</v>
       </c>
       <c r="C8" s="4" t="inlineStr">
         <is>
@@ -2842,12 +3327,12 @@
         </is>
       </c>
       <c r="B12" s="8">
-        <f>B5*B6</f>
+        <f>Orçar!C27</f>
         <v/>
       </c>
       <c r="C12" s="4" t="inlineStr">
         <is>
-          <t>BAC x % planejado</t>
+          <t>Curva S (aba Orçar)</t>
         </is>
       </c>
     </row>
@@ -3021,7 +3506,7 @@
     <row r="25" ht="96" customHeight="1">
       <c r="A25" s="15" t="inlineStr">
         <is>
-          <t>No ritmo atual o projeto está levemente acima do orçamento (CPI ~0,96) e atrasado (SPI ~0,92). A projeção de término (EAC ~R$ 32.002) fura a linha de base em ~R$ 1.312, consumindo quase toda a reserva de gerenciamento (R$ 1.535). Pela tolerância definida na aba Planejar, ainda não é escalonamento imediato, mas dispara revisão formal e coloca o patrocinador em alerta. A ação corretiva se concentra no maior risco do caminho crítico — o Motor de alertas (atividade A8 do Cronograma). O TCPI ~1,06 exige o trabalho restante ~6% mais eficiente que o planejado. A decisão olha a TENDÊNCIA do CPI ao longo dos check-ins, não a foto de uma semana.</t>
+          <t>No ritmo atual o projeto está levemente acima do orçamento (CPI ~0,96) e atrasado (SPI ~0,92). A projeção de término (EAC ~R$ 34.194) fura a linha de base em ~R$ 1.424, o equivalente a 87% da reserva de gerenciamento (R$ 1.639). Pela tolerância definida na aba Planejar, ainda não é escalonamento imediato, mas dispara revisão formal e coloca o patrocinador em alerta. A ação corretiva se concentra no maior risco do caminho crítico — o Motor de alertas (atividade A8 do Cronograma). O TCPI ~1,08 exige o trabalho restante ~8% mais eficiente que o planejado. A decisão olha a TENDÊNCIA do CPI ao longo dos check-ins, não a foto de uma semana.</t>
         </is>
       </c>
     </row>
@@ -3056,7 +3541,7 @@
           <t>A reserva de gerenciamento fica fora da linha de base; o EVM compara sempre contra o BAC, nunca contra o orçamento total.</t>
         </is>
       </c>
-      <c r="C29" s="6" t="n"/>
+      <c r="C29" s="5" t="n"/>
     </row>
     <row r="30" ht="30" customHeight="1">
       <c r="A30" s="4" t="inlineStr">
@@ -3069,7 +3554,7 @@
           <t>Termina em 'Índice' divide; termina em 'Variação' subtrai. SV/SPI em reais, não em dias.</t>
         </is>
       </c>
-      <c r="C30" s="6" t="n"/>
+      <c r="C30" s="5" t="n"/>
     </row>
     <row r="31" ht="30" customHeight="1">
       <c r="A31" s="4" t="inlineStr">
@@ -3082,7 +3567,7 @@
           <t>Para CPI/SPI, &lt;1 é ruim; para o TCPI, &gt;1 é o difícil (trabalho restante mais eficiente).</t>
         </is>
       </c>
-      <c r="C31" s="6" t="n"/>
+      <c r="C31" s="5" t="n"/>
     </row>
     <row r="32" ht="30" customHeight="1">
       <c r="A32" s="4" t="inlineStr">
@@ -3095,7 +3580,7 @@
           <t>O documento mede também o valor entregue (ROI, VPL, TIR, payback) na aba Gerenciar.</t>
         </is>
       </c>
-      <c r="C32" s="6" t="n"/>
+      <c r="C32" s="5" t="n"/>
     </row>
     <row r="33" ht="30" customHeight="1">
       <c r="A33" s="4" t="inlineStr">
@@ -3108,7 +3593,7 @@
           <t>A medição começa no dia 1, no mesmo check-in semanal, com a janela de intervenção aberta.</t>
         </is>
       </c>
-      <c r="C33" s="6" t="n"/>
+      <c r="C33" s="5" t="n"/>
     </row>
     <row r="34" ht="30" customHeight="1">
       <c r="A34" s="4" t="inlineStr">
@@ -3121,7 +3606,7 @@
           <t>Cada indicador vem com a decisão que dispara — dado sem decisão não é controle.</t>
         </is>
       </c>
-      <c r="C34" s="6" t="n"/>
+      <c r="C34" s="5" t="n"/>
     </row>
     <row r="35" ht="30" customHeight="1">
       <c r="A35" s="4" t="inlineStr">
@@ -3131,10 +3616,10 @@
       </c>
       <c r="B35" s="4" t="inlineStr">
         <is>
-          <t>Como o desvio é variação típica, EAC = BAC / CPI (e não a fórmula de evento único).</t>
-        </is>
-      </c>
-      <c r="C35" s="6" t="n"/>
+          <t>Como o desvio é variação típica, EAC = BAC / CPI. Evento único: AC + (BAC - EV). Pessimista (custo e prazo pesam juntos): AC + (BAC - EV) / (CPI x SPI).</t>
+        </is>
+      </c>
+      <c r="C35" s="5" t="n"/>
     </row>
   </sheetData>
   <mergeCells count="14">
